--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-05).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-05).xlsx
@@ -1020,35 +1020,27 @@
           <t>DINAS PEKERJAAN UMUM DAN PENATAAN RUANG - 1.03.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>1796500000</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1389,22 +1381,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>677290237</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>137583844</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>116218702</v>
+        <v>1301651478</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>90</v>
@@ -1528,13 +1520,13 @@
         <v>173</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2228006763</v>
+        <v>2218502610</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>54</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1136240668</v>
+        <v>1126736515</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>54</v>
@@ -1868,13 +1860,13 @@
         <v>112</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1305525621</v>
+        <v>1279995621</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>18</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>378058156</v>
+        <v>352528156</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>18</v>
@@ -2035,22 +2027,22 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D44" s="9" t="n">
         <v>282819298</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>141795000</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>64745634</v>
+        <v>121094174</v>
       </c>
       <c r="I44" s="7" t="n">
         <v>17</v>
@@ -3363,22 +3355,22 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>3940</v>
+        <v>3967</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>32741811564</v>
+        <v>32706777411</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>6693854006</v>
+        <v>6658819853</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>6159636368.6</v>
+        <v>9197917684.6</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>3523</v>
@@ -5584,28 +5576,28 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>595373450</v>
+        <v>379426400</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>417917650</v>
+        <v>201970600</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>198768000</v>
+        <v>142419460</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>198768000</v>
+        <v>142419460</v>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
@@ -7536,28 +7528,28 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>97389641039</v>
+        <v>97173693989</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>64871532693</v>
+        <v>64655585643</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>63154109969.41</v>
+        <v>63097761429.41</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>33555205925</v>
+        <v>33498857385</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>12</v>
@@ -8371,28 +8363,28 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>26735477939</v>
+        <v>25286544212</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>26735477939</v>
+        <v>25286544212</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>26035273641</v>
+        <v>24238773641</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>26035273641</v>
+        <v>24238773641</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
@@ -8590,13 +8582,13 @@
         <v>1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>1269914370</v>
+        <v>634957185</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1269914370</v>
+        <v>634957185</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>1</v>
@@ -8815,34 +8807,34 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>48003814160</v>
+        <v>5652342335</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>47632716881</v>
+        <v>5281245056</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>4157004750</v>
+        <v>2971571974</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>4157004750</v>
+        <v>2971571974</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>2945468782</v>
+        <v>1854621974</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>1</v>
@@ -12013,34 +12005,34 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>179606321958</v>
+        <v>135170959221</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>143234386443</v>
+        <v>98799023706</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>69752277713.01001</v>
+        <v>66770344937.01</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>65303843913</v>
+        <v>62321911137</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>4005987066</v>
+        <v>2915140258</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>79</v>

--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-05).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-05).xlsx
@@ -1020,27 +1020,35 @@
           <t>DINAS PEKERJAAN UMUM DAN PENATAAN RUANG - 1.03.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>1</v>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>1</v>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>1796500000</v>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1381,22 +1389,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>677290237</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>137583844</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>1301651478</v>
+        <v>116218702</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>90</v>
@@ -1520,13 +1528,13 @@
         <v>173</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2218502610</v>
+        <v>2228006763</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>54</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1126736515</v>
+        <v>1136240668</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>54</v>
@@ -1860,13 +1868,13 @@
         <v>112</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1279995621</v>
+        <v>1305525621</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>18</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>352528156</v>
+        <v>378058156</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>18</v>
@@ -2027,22 +2035,22 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D44" s="9" t="n">
         <v>282819298</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>141795000</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>121094174</v>
+        <v>64745634</v>
       </c>
       <c r="I44" s="7" t="n">
         <v>17</v>
@@ -3355,22 +3363,22 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>3967</v>
+        <v>3940</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>32706777411</v>
+        <v>32741811564</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>6658819853</v>
+        <v>6693854006</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>9197917684.6</v>
+        <v>6159636368.6</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>3523</v>
@@ -5576,28 +5584,28 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>595373450</v>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="9" t="n">
-        <v>379426400</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="F44" s="9" t="n">
-        <v>201970600</v>
+        <v>417917650</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>142419460</v>
+        <v>198768000</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>142419460</v>
+        <v>198768000</v>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
@@ -7528,28 +7536,28 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>97173693989</v>
+        <v>97389641039</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>64655585643</v>
+        <v>64871532693</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>63097761429.41</v>
+        <v>63154109969.41</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>33498857385</v>
+        <v>33555205925</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>12</v>
@@ -8363,28 +8371,28 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>25286544212</v>
+        <v>26735477939</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>25286544212</v>
+        <v>26735477939</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>24238773641</v>
+        <v>26035273641</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>24238773641</v>
+        <v>26035273641</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
@@ -8582,13 +8590,13 @@
         <v>1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>634957185</v>
+        <v>1269914370</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>634957185</v>
+        <v>1269914370</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>1</v>
@@ -8807,34 +8815,34 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>5652342335</v>
+        <v>48003814160</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5281245056</v>
+        <v>47632716881</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>2971571974</v>
+        <v>4157004750</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>2971571974</v>
+        <v>4157004750</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>1854621974</v>
+        <v>2945468782</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>1</v>
@@ -12005,34 +12013,34 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>135170959221</v>
+        <v>179606321958</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>98799023706</v>
+        <v>143234386443</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>66770344937.01</v>
+        <v>69752277713.01001</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>62321911137</v>
+        <v>65303843913</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>2915140258</v>
+        <v>4005987066</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>79</v>

--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-05).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-05).xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>291008487</v>
+        <v>4500000</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="I10" s="7" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>291008487</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>381815300</v>
+        <v>56143000</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>3</v>
@@ -810,11 +810,15 @@
       <c r="H11" s="11" t="n">
         <v>56143000</v>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>325672300</v>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -826,11 +830,15 @@
           <t>Badan Keuangan dan Aset Daerah - 5.02.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>694885745</v>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -852,11 +860,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>694885745</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -869,10 +881,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>494143453</v>
+        <v>19928718</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2</v>
@@ -886,11 +898,15 @@
       <c r="H13" s="11" t="n">
         <v>16692513</v>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>474214735</v>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -903,10 +919,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>732115182</v>
+        <v>169489998</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>5</v>
@@ -920,11 +936,15 @@
       <c r="H14" s="9" t="n">
         <v>164526300</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>562625184</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -937,10 +957,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>777986001</v>
+        <v>63250745</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>2</v>
@@ -954,11 +974,15 @@
       <c r="H15" s="11" t="n">
         <v>62335938</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>714735256</v>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -1321,10 +1345,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>837899282</v>
+        <v>59461794</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>5</v>
@@ -1338,11 +1362,15 @@
       <c r="H23" s="11" t="n">
         <v>59317658</v>
       </c>
-      <c r="I23" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>778437488</v>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1355,10 +1383,10 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>491911485</v>
+        <v>84907554</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>5</v>
@@ -1372,11 +1400,15 @@
       <c r="H24" s="9" t="n">
         <v>78869208</v>
       </c>
-      <c r="I24" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>407003931</v>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -1389,10 +1421,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>677290237</v>
+        <v>137583844</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>13</v>
@@ -1406,11 +1438,15 @@
       <c r="H25" s="11" t="n">
         <v>116218702</v>
       </c>
-      <c r="I25" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>539706393</v>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -1423,10 +1459,10 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>553370393</v>
+        <v>350423349</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>17</v>
@@ -1440,11 +1476,15 @@
       <c r="H26" s="9" t="n">
         <v>350174900</v>
       </c>
-      <c r="I26" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>202947044</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -1457,10 +1497,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>127</v>
+        <v>39</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>908204422</v>
+        <v>350117338</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>39</v>
@@ -1474,11 +1514,15 @@
       <c r="H27" s="11" t="n">
         <v>326386463</v>
       </c>
-      <c r="I27" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>558087084</v>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -1491,10 +1535,10 @@
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>780728426</v>
+        <v>38508000</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>1</v>
@@ -1508,11 +1552,15 @@
       <c r="H28" s="9" t="n">
         <v>38508000</v>
       </c>
-      <c r="I28" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>742220426</v>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -1525,10 +1573,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2228006763</v>
+        <v>1171240668</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>54</v>
@@ -1543,10 +1591,10 @@
         <v>1115612710.6</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>1091766095</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -1559,10 +1607,10 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>444206345</v>
+        <v>79101092</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>6</v>
@@ -1576,11 +1624,15 @@
       <c r="H30" s="9" t="n">
         <v>75945607</v>
       </c>
-      <c r="I30" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>365105253</v>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -1593,10 +1645,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>342136823</v>
+        <v>30262050</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>5</v>
@@ -1610,11 +1662,15 @@
       <c r="H31" s="11" t="n">
         <v>26778260</v>
       </c>
-      <c r="I31" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>311874773</v>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -1627,10 +1683,10 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>794109241</v>
+        <v>107342366</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>6</v>
@@ -1644,11 +1700,15 @@
       <c r="H32" s="9" t="n">
         <v>101626500</v>
       </c>
-      <c r="I32" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>686766875</v>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -1661,10 +1721,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>304521329</v>
+        <v>108974684</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>5</v>
@@ -1678,11 +1738,15 @@
       <c r="H33" s="11" t="n">
         <v>52571289</v>
       </c>
-      <c r="I33" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>195546645</v>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -1695,10 +1759,10 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2184236820</v>
+        <v>617822537</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>38</v>
@@ -1713,10 +1777,10 @@
         <v>332486817</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1847861183</v>
+        <v>281446900</v>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -1729,10 +1793,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>418455903</v>
+        <v>93366423</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>6</v>
@@ -1746,11 +1810,15 @@
       <c r="H35" s="11" t="n">
         <v>92923430</v>
       </c>
-      <c r="I35" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>325089480</v>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -1763,10 +1831,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>859678273</v>
+        <v>373368532</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>13</v>
@@ -1781,10 +1849,10 @@
         <v>330804697</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>525334455</v>
+        <v>39024714</v>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -1797,10 +1865,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>858385693</v>
+        <v>461686502</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>16</v>
@@ -1814,11 +1882,15 @@
       <c r="H37" s="11" t="n">
         <v>451166160</v>
       </c>
-      <c r="I37" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>396699191</v>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -1831,10 +1903,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>353593331</v>
+        <v>87341338</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>11</v>
@@ -1848,11 +1920,15 @@
       <c r="H38" s="9" t="n">
         <v>72817850</v>
       </c>
-      <c r="I38" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>266251993</v>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -1865,10 +1941,10 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1305525621</v>
+        <v>378058156</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>18</v>
@@ -1882,11 +1958,15 @@
       <c r="H39" s="11" t="n">
         <v>374723886</v>
       </c>
-      <c r="I39" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>927467465</v>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -1899,10 +1979,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>890594163</v>
+        <v>613053005</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>27</v>
@@ -1916,11 +1996,15 @@
       <c r="H40" s="9" t="n">
         <v>518537008</v>
       </c>
-      <c r="I40" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>277541158</v>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -1933,10 +2017,10 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>744929925</v>
+        <v>73061846</v>
       </c>
       <c r="E41" s="4" t="n">
         <v>16</v>
@@ -1950,11 +2034,15 @@
       <c r="H41" s="11" t="n">
         <v>66608150</v>
       </c>
-      <c r="I41" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>671868079</v>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -1967,10 +2055,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>550936395</v>
+        <v>73983300</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>6</v>
@@ -1984,11 +2072,15 @@
       <c r="H42" s="9" t="n">
         <v>73788167</v>
       </c>
-      <c r="I42" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>476953095</v>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
@@ -2001,10 +2093,10 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>489056792</v>
+        <v>34949904</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>3</v>
@@ -2018,11 +2110,15 @@
       <c r="H43" s="11" t="n">
         <v>21152715</v>
       </c>
-      <c r="I43" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>454106888</v>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -2035,10 +2131,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>282819298</v>
+        <v>141795000</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>4</v>
@@ -2052,11 +2148,15 @@
       <c r="H44" s="9" t="n">
         <v>64745634</v>
       </c>
-      <c r="I44" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>141024298</v>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -2119,10 +2219,10 @@
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1076116871</v>
+        <v>219732901</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>10</v>
@@ -2137,10 +2237,10 @@
         <v>121983128</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>951143970</v>
+        <v>94760000</v>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -2149,14 +2249,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D47" s="11" t="n">
-        <v>310252566</v>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
@@ -2178,11 +2282,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>310252566</v>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -2191,40 +2299,32 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>382528466</v>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>239748425</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>204940123</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>182303900</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>382528466</v>
+        <v>34808302</v>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -2233,32 +2333,48 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>619121476</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>204940123</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H49" s="11" t="n">
-        <v>182303900</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>414181353</v>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
@@ -2267,14 +2383,14 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>175284644</v>
+        <v>31600000</v>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
@@ -2297,10 +2413,10 @@
         </is>
       </c>
       <c r="I50" s="7" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>175284644</v>
+        <v>31600000</v>
       </c>
     </row>
     <row r="51" ht="45" customHeight="1">
@@ -2309,14 +2425,14 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>219851775</v>
+        <v>21000000</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
@@ -2339,10 +2455,10 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>219851775</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="52" ht="45" customHeight="1">
@@ -2351,14 +2467,18 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D52" s="9" t="n">
-        <v>166377553</v>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
@@ -2380,11 +2500,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="J52" s="9" t="n">
-        <v>166377553</v>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="45" customHeight="1">
@@ -2393,40 +2517,36 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>463616007</v>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>463616007</v>
+        <v>66380633</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>66380633</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>15724250</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
@@ -2435,40 +2555,36 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>51896600</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>51896600</v>
+        <v>35716900</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>35716900</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>26129400</v>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="45" customHeight="1">
@@ -2477,40 +2593,34 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>183754320</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>108000000</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>72150000</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J55" s="11" t="n">
-        <v>183754320</v>
+        <v>1</v>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="45" customHeight="1">
@@ -2519,14 +2629,18 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="D56" s="9" t="n">
-        <v>489429711</v>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
@@ -2548,11 +2662,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>489429711</v>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="45" customHeight="1">
@@ -2561,40 +2679,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>196969887</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>129198291</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>115323291</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>113833150</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>196969887</v>
+        <v>13875000</v>
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
@@ -2603,40 +2713,32 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>397703689</v>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>454274186</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>419874186</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>414065940</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>397703689</v>
+        <v>34400000</v>
       </c>
     </row>
     <row r="59" ht="45" customHeight="1">
@@ -2645,746 +2747,68 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>319912312</v>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>319912312</v>
+        <v>198895843</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>198895843</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>171985038</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D60" s="9" t="n">
-        <v>138079030</v>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J60" s="9" t="n">
-        <v>138079030</v>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="D61" s="11" t="n">
-        <v>411198562</v>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>411198562</v>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="D62" s="9" t="n">
-        <v>387164122</v>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>387164122</v>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D63" s="11" t="n">
-        <v>289499767</v>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J63" s="11" t="n">
-        <v>289499767</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D64" s="9" t="n">
-        <v>240267455</v>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>240267455</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D65" s="11" t="n">
-        <v>153251633</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>66380633</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H65" s="11" t="n">
-        <v>15724250</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="n">
-        <v>86871000</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D66" s="9" t="n">
-        <v>186180796</v>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="J66" s="9" t="n">
-        <v>186180796</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D67" s="11" t="n">
-        <v>121367900</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J67" s="11" t="n">
-        <v>121367900</v>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="D68" s="9" t="n">
-        <v>378945500</v>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="J68" s="9" t="n">
-        <v>378945500</v>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D69" s="11" t="n">
-        <v>382606656</v>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J69" s="11" t="n">
-        <v>382606656</v>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D70" s="9" t="n">
-        <v>179964901</v>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>179964901</v>
-      </c>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D71" s="11" t="n">
-        <v>345486342</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" s="11" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" s="11" t="n">
-        <v>26129400</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="J71" s="11" t="n">
-        <v>309769442</v>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>637283463</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F72" s="9" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>72150000</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>529283463</v>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
-      <c r="A74" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D74" s="9" t="n">
-        <v>354293991</v>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>115323291</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H74" s="9" t="n">
-        <v>113833150</v>
-      </c>
-      <c r="I74" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>238970700</v>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D75" s="11" t="n">
-        <v>1314919871</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F75" s="11" t="n">
-        <v>419874186</v>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H75" s="11" t="n">
-        <v>414065940</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="J75" s="11" t="n">
-        <v>895045685</v>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="n">
-        <v>156</v>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>1495934570</v>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>198895843</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>171985038</v>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>131</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>1297038727</v>
-      </c>
-    </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C77" s="12" t="n">
-        <v>3940</v>
-      </c>
-      <c r="D77" s="13" t="n">
-        <v>32741811564</v>
-      </c>
-      <c r="E77" s="12" t="n">
+      <c r="C60" s="12" t="n">
+        <v>449</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>7284268922</v>
+      </c>
+      <c r="E60" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F60" s="13" t="n">
         <v>6693854006</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="H77" s="13" t="n">
+      <c r="H60" s="13" t="n">
         <v>6159636368.6</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>3523</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>26047957558</v>
+      <c r="I60" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>590414916</v>
       </c>
     </row>
   </sheetData>
@@ -3416,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3740,10 +3164,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>259388320</v>
+        <v>59000000</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -3786,10 +3210,10 @@
         </is>
       </c>
       <c r="M10" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>259388320</v>
+        <v>59000000</v>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -3802,10 +3226,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>448925330</v>
+        <v>276710330</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>3</v>
@@ -3835,11 +3259,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>172215000</v>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -3852,10 +3280,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>484082242</v>
+        <v>168902040</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1</v>
@@ -3885,11 +3313,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>315180202</v>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -3902,10 +3334,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>669448547</v>
+        <v>239139830</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>3</v>
@@ -3931,11 +3363,15 @@
       <c r="L13" s="11" t="n">
         <v>57714450</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" s="11" t="n">
-        <v>430308717</v>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -3948,10 +3384,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1559854479</v>
+        <v>1017935443</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>7</v>
@@ -3982,10 +3418,10 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>849541276</v>
+        <v>307622240</v>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -4510,10 +3946,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>957216782</v>
+        <v>138750000</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
@@ -4543,11 +3979,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N23" s="11" t="n">
-        <v>818466782</v>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -4560,10 +4000,10 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>266301572</v>
+        <v>54773006</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>1</v>
@@ -4589,11 +4029,15 @@
       <c r="L24" s="9" t="n">
         <v>49345050</v>
       </c>
-      <c r="M24" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>211528566</v>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -4606,10 +4050,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1566751699</v>
+        <v>1225542538</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>12</v>
@@ -4635,11 +4079,15 @@
       <c r="L25" s="11" t="n">
         <v>290793365</v>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" s="11" t="n">
-        <v>341209161</v>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -4652,10 +4100,10 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1109929988</v>
+        <v>873381088</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>10</v>
@@ -4686,10 +4134,10 @@
         </is>
       </c>
       <c r="M26" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>292304988</v>
+        <v>55756088</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -4702,10 +4150,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1888168641</v>
+        <v>1162285000</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>7</v>
@@ -4736,10 +4184,10 @@
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>921188141</v>
+        <v>195304500</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -4752,10 +4200,10 @@
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1542962774</v>
+        <v>604952000</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>3</v>
@@ -4786,10 +4234,10 @@
         </is>
       </c>
       <c r="M28" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>1113010774</v>
+        <v>175000000</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -4802,10 +4250,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>19451882505</v>
+        <v>15522703657</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>112</v>
@@ -4831,11 +4279,15 @@
       <c r="L29" s="11" t="n">
         <v>72965295</v>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="N29" s="11" t="n">
-        <v>3929178848</v>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -4848,10 +4300,10 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>376694000</v>
+        <v>288750000</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2</v>
@@ -4881,11 +4333,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="9" t="n">
-        <v>87944000</v>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -4898,10 +4354,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>405798874</v>
+        <v>66310000</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>1</v>
@@ -4931,11 +4387,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="11" t="n">
-        <v>339488874</v>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -4948,10 +4408,10 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>610038436</v>
+        <v>333375600</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>3</v>
@@ -4981,11 +4441,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>276662836</v>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -5052,10 +4516,10 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>6465227440</v>
+        <v>4651711884</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>33</v>
@@ -5086,10 +4550,10 @@
         </is>
       </c>
       <c r="M34" s="7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>2457728456</v>
+        <v>644212900</v>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -5102,10 +4566,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1177904322</v>
+        <v>913021368</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>7</v>
@@ -5135,11 +4599,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" s="11" t="n">
-        <v>264882954</v>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -5152,10 +4620,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>5044708697</v>
+        <v>4615918940</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>32</v>
@@ -5186,10 +4654,10 @@
         </is>
       </c>
       <c r="M36" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>971955825</v>
+        <v>543166068</v>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -5202,10 +4670,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>2672104510</v>
+        <v>2025090451</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>17</v>
@@ -5232,10 +4700,10 @@
         <v>313637363</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>926734059</v>
+        <v>279720000</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -5247,11 +4715,15 @@
           <t>Dinas Perpustakaan dan Kearsipan - 2.23.2.24.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>190561024</v>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -5293,11 +4765,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N38" s="9" t="n">
-        <v>190561024</v>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -5310,10 +4786,10 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>4842583639</v>
+        <v>2769384586</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>24</v>
@@ -5339,11 +4815,15 @@
       <c r="L39" s="11" t="n">
         <v>94888350</v>
       </c>
-      <c r="M39" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="N39" s="11" t="n">
-        <v>2073199053</v>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -5356,10 +4836,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>24100076698</v>
+        <v>23567530878</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>175</v>
@@ -5389,11 +4869,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N40" s="9" t="n">
-        <v>532545820</v>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -5406,10 +4890,10 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1113387305</v>
+        <v>69750000</v>
       </c>
       <c r="E41" s="4" t="n">
         <v>1</v>
@@ -5443,11 +4927,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M41" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="N41" s="11" t="n">
-        <v>1043637305</v>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -5459,11 +4947,15 @@
           <t>Dinas Tenaga Kerja dan Transmigrasi - 2.07.3.32.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>346039368</v>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -5505,11 +4997,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N42" s="9" t="n">
-        <v>346039368</v>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
@@ -5521,11 +5017,15 @@
           <t>Inspektorat Daerah - 6.01.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>470786500</v>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
@@ -5567,11 +5067,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N43" s="11" t="n">
-        <v>470786500</v>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -5584,10 +5088,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>595373450</v>
+        <v>417917650</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>5</v>
@@ -5617,11 +5121,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" s="9" t="n">
-        <v>177455800</v>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -5704,10 +5212,10 @@
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>835283701</v>
+        <v>471330601</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>6</v>
@@ -5737,11 +5245,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N46" s="9" t="n">
-        <v>363953100</v>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -5750,14 +5262,18 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="11" t="n">
-        <v>154997000</v>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
@@ -5799,11 +5315,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="11" t="n">
-        <v>154997000</v>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -5812,44 +5332,32 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>124841500</v>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>214759000</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>81320000</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>80619300</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>80619300</v>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
@@ -5865,7 +5373,7 @@
         <v>2</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>124841500</v>
+        <v>133439000</v>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -5874,32 +5382,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>320725524</v>
+        <v>71700000</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>81320000</v>
+        <v>71700000</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>80619300</v>
+        <v>71700000</v>
       </c>
       <c r="I49" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>80619300</v>
+        <v>71700000</v>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
@@ -5911,11 +5419,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" s="11" t="n">
-        <v>239405524</v>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
@@ -5924,32 +5436,32 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>137310832</v>
+        <v>340582172</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>71700000</v>
+        <v>340582172</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>71700000</v>
+        <v>68020787</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>71700000</v>
+        <v>68020787</v>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
@@ -5961,11 +5473,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="9" t="n">
-        <v>65610832</v>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="45" customHeight="1">
@@ -5974,7 +5490,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6044,32 +5560,32 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>403460838</v>
+        <v>348491630</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>340582172</v>
+        <v>153891630</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>68020787</v>
+        <v>53835000</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>68020787</v>
+        <v>53835000</v>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
@@ -6085,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>62878666</v>
+        <v>194600000</v>
       </c>
     </row>
     <row r="53" ht="45" customHeight="1">
@@ -6094,14 +5610,18 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D53" s="11" t="n">
-        <v>305850296</v>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
@@ -6143,11 +5663,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N53" s="11" t="n">
-        <v>305850296</v>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
@@ -6156,44 +5680,32 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>212926585</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>146817603</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>146817603</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>43541637</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>43541637</v>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
@@ -6205,11 +5717,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N54" s="9" t="n">
-        <v>212926585</v>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="45" customHeight="1">
@@ -6218,44 +5734,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>154700000</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50400000</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>49950000</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>49950000</v>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
@@ -6267,11 +5771,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" s="11" t="n">
-        <v>154700000</v>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="45" customHeight="1">
@@ -6280,14 +5788,18 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D56" s="9" t="n">
-        <v>397980729</v>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
@@ -6329,11 +5841,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N56" s="9" t="n">
-        <v>397980729</v>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="45" customHeight="1">
@@ -6342,44 +5858,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>145950000</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>205350000</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>55500000</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>55100000</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>55100000</v>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
@@ -6392,10 +5896,10 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" s="11" t="n">
-        <v>145950000</v>
+        <v>149850000</v>
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
@@ -6404,44 +5908,32 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>494958640</v>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1765832056</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>1415832056</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>1411155433</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>1282055107</v>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
@@ -6454,10 +5946,10 @@
         </is>
       </c>
       <c r="M58" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N58" s="9" t="n">
-        <v>494958640</v>
+        <v>350000000</v>
       </c>
     </row>
     <row r="59" ht="45" customHeight="1">
@@ -6466,44 +5958,32 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>189350000</v>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>815487047</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>639698247</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>626374825</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>552004825</v>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
@@ -6519,1057 +5999,51 @@
         <v>2</v>
       </c>
       <c r="N59" s="11" t="n">
-        <v>189350000</v>
+        <v>175788800</v>
       </c>
     </row>
     <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="9" t="n">
-        <v>235342500</v>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N60" s="9" t="n">
-        <v>235342500</v>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" s="11" t="n">
-        <v>141393225</v>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N61" s="11" t="n">
-        <v>141393225</v>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" s="9" t="n">
-        <v>348491630</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>153891630</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="9" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="I62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" s="9" t="n">
-        <v>194600000</v>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" s="9" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" s="9" t="n">
-        <v>189000000</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="9" t="n">
-        <v>143150000</v>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="9" t="n">
-        <v>143150000</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="11" t="n">
-        <v>149292000</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" s="11" t="n">
-        <v>149292000</v>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D68" s="9" t="n">
-        <v>275450000</v>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M68" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N68" s="9" t="n">
-        <v>275450000</v>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="11" t="n">
-        <v>66272893</v>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" s="11" t="n">
-        <v>66272893</v>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D70" s="9" t="n">
-        <v>175130000</v>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M70" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N70" s="9" t="n">
-        <v>175130000</v>
-      </c>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D71" s="11" t="n">
-        <v>647501699</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="11" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="11" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="11" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="K71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N71" s="11" t="n">
-        <v>500684096</v>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>3366887490</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="9" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="K72" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M72" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="N72" s="9" t="n">
-        <v>3316487490</v>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
-      <c r="A74" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D74" s="9" t="n">
-        <v>463002876</v>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>55500000</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="9" t="n">
-        <v>55100000</v>
-      </c>
-      <c r="I74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>55100000</v>
-      </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N74" s="9" t="n">
-        <v>407502876</v>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D75" s="11" t="n">
-        <v>2759430816</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F75" s="11" t="n">
-        <v>1415832056</v>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H75" s="11" t="n">
-        <v>1411155433</v>
-      </c>
-      <c r="I75" s="4" t="n">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL KESELURUHAN</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>538</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>68134992289</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>513</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>64871532693</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>513</v>
+      </c>
+      <c r="H60" s="13" t="n">
+        <v>63154109969.41</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>280</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>33555205925</v>
+      </c>
+      <c r="K60" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J75" s="11" t="n">
-        <v>1282055107</v>
-      </c>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N75" s="11" t="n">
-        <v>1343598760</v>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>3293357232</v>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>639698247</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>626374825</v>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>552004825</v>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>2653658985</v>
-      </c>
-    </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL KESELURUHAN</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="n">
-        <v>823</v>
-      </c>
-      <c r="D77" s="13" t="n">
-        <v>97389641039</v>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v>513</v>
-      </c>
-      <c r="F77" s="13" t="n">
-        <v>64871532693</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>513</v>
-      </c>
-      <c r="H77" s="13" t="n">
-        <v>63154109969.41</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>280</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>33555205925</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L77" s="13" t="n">
+      <c r="L60" s="13" t="n">
         <v>879343873</v>
       </c>
-      <c r="M77" s="12" t="n">
-        <v>310</v>
-      </c>
-      <c r="N77" s="13" t="n">
-        <v>32518108346</v>
+      <c r="M60" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>3263459596</v>
       </c>
     </row>
   </sheetData>
@@ -7601,7 +6075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8072,11 +6546,15 @@
           <t>Badan Keuangan dan Aset Daerah - 5.02.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>206878992</v>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -8118,11 +6596,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>206878992</v>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -8205,10 +6687,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1344967600</v>
+        <v>1128517600</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1</v>
@@ -8239,10 +6721,10 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>1128517600</v>
+        <v>912067600</v>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -8254,11 +6736,15 @@
           <t>Badan Perencanaan Pembangunan, Riset dan Inovasi Daerah - 5.01.5.05.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>217952667</v>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -8300,11 +6786,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>217952667</v>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -8702,11 +7192,15 @@
           <t>Dinas Kepemudaan dan Olahraga - 2.19.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>658884360</v>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
@@ -8748,11 +7242,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="11" t="n">
-        <v>658884360</v>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -8815,10 +7313,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>48003814160</v>
+        <v>47632716881</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>32</v>
@@ -8844,11 +7342,15 @@
       <c r="L25" s="11" t="n">
         <v>2945468782</v>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="11" t="n">
-        <v>371097279</v>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -8931,10 +7433,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>6129521900</v>
+        <v>3459514800</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>4</v>
@@ -8964,11 +7466,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="11" t="n">
-        <v>2670007100</v>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -9035,10 +7541,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>11271370446</v>
+        <v>7543626094</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>22</v>
@@ -9068,11 +7574,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N29" s="11" t="n">
-        <v>3727744352</v>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -9085,10 +7595,10 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1366776000</v>
+        <v>1086690000</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2</v>
@@ -9118,11 +7628,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="9" t="n">
-        <v>280086000</v>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -9134,11 +7648,15 @@
           <t>Dinas Pemberdayaan Masyarakat dan Desa - 2.13.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>914760000</v>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
@@ -9180,11 +7698,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="11" t="n">
-        <v>914760000</v>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -9196,11 +7718,15 @@
           <t>Dinas Pemberdayaan Perempuan dan Perlindungan Anak, Pengendalian Penduduk dan Keluarga Berencana - 2.08.2.14.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>312000000</v>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -9242,11 +7768,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>312000000</v>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -9258,11 +7788,15 @@
           <t>Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu - 2.18.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>205076880</v>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
@@ -9304,11 +7838,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="11" t="n">
-        <v>205076880</v>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -9321,10 +7859,10 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2966457340</v>
+        <v>2359342000</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>4</v>
@@ -9355,10 +7893,10 @@
         </is>
       </c>
       <c r="M34" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1863119340</v>
+        <v>1256004000</v>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -9370,11 +7908,15 @@
           <t>Dinas Perhubungan - 2.15.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>527433456</v>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
@@ -9416,11 +7958,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" s="11" t="n">
-        <v>527433456</v>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -9433,10 +7979,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2208956507</v>
+        <v>1763376386</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>7</v>
@@ -9466,11 +8012,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" s="9" t="n">
-        <v>445580121</v>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -9483,10 +8033,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4247240896</v>
+        <v>2946694000</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>3</v>
@@ -9512,11 +8062,15 @@
       <c r="L37" s="11" t="n">
         <v>436796630</v>
       </c>
-      <c r="M37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" s="11" t="n">
-        <v>1300546896</v>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -9599,10 +8153,10 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>3813601480</v>
+        <v>3258841480</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>9</v>
@@ -9633,10 +8187,10 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>799760000</v>
+        <v>245000000</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -9649,10 +8203,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>3004707600</v>
+        <v>2516796000</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>9</v>
@@ -9682,11 +8236,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" s="9" t="n">
-        <v>487911600</v>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -10039,18 +8597,14 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>440899992</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
@@ -10092,15 +8646,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>440899992</v>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -10109,14 +8659,18 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>440899992</v>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
@@ -10158,11 +8712,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" s="9" t="n">
-        <v>440899992</v>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -10171,7 +8729,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -10241,7 +8799,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -10311,7 +8869,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -10381,14 +8939,18 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="9" t="n">
-        <v>1937370950</v>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
@@ -10430,11 +8992,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="9" t="n">
-        <v>1937370950</v>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="45" customHeight="1">
@@ -10443,14 +9009,18 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="11" t="n">
-        <v>1032445697</v>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
@@ -10492,11 +9062,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" s="11" t="n">
-        <v>1032445697</v>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
@@ -10505,14 +9079,18 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="9" t="n">
-        <v>456516000</v>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
@@ -10554,11 +9132,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" s="9" t="n">
-        <v>456516000</v>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="45" customHeight="1">
@@ -10567,58 +9149,38 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>8054692000</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>8054692000</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>2808340212</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>2808340212</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>64551162</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -10637,48 +9199,32 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>3728971961</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>3728971961</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>3662300000</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>3662300000</v>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
@@ -10707,7 +9253,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -10777,44 +9323,32 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>223700000</v>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>218268000</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>218268000</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>185076000</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>185076000</v>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
@@ -10826,11 +9360,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" s="9" t="n">
-        <v>223700000</v>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="45" customHeight="1">
@@ -10839,48 +9377,32 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>3294207800</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>2944207800</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>2058441500</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>2058441500</v>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
@@ -10892,1161 +9414,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="11" t="n">
+        <v>350000000</v>
       </c>
     </row>
     <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>13928798637</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" s="9" t="n">
-        <v>8054692000</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>2808340212</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>2808340212</v>
-      </c>
-      <c r="K72" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" s="9" t="n">
-        <v>64551162</v>
-      </c>
-      <c r="M72" s="7" t="n">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL KESELURUHAN</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>149894693435</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>158</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>143234386443</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>158</v>
+      </c>
+      <c r="H60" s="13" t="n">
+        <v>69752277713.01001</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>65303843913</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>4005987066</v>
+      </c>
+      <c r="M60" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N72" s="9" t="n">
-        <v>5874106637</v>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" s="11" t="n">
-        <v>3728971961</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" s="11" t="n">
-        <v>3728971961</v>
-      </c>
-      <c r="G73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H73" s="11" t="n">
-        <v>3662300000</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="11" t="n">
-        <v>3662300000</v>
-      </c>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
-      <c r="A74" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="9" t="n">
-        <v>211404000</v>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="9" t="n">
-        <v>211404000</v>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D75" s="11" t="n">
-        <v>1302319040</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="11" t="n">
-        <v>218268000</v>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="11" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="11" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" s="11" t="n">
-        <v>1084051040</v>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>8481956956</v>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>2944207800</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>2058441500</v>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>2058441500</v>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>5537749156</v>
-      </c>
-    </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL KESELURUHAN</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="n">
-        <v>237</v>
-      </c>
-      <c r="D77" s="13" t="n">
-        <v>179606321958</v>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v>158</v>
-      </c>
-      <c r="F77" s="13" t="n">
-        <v>143234386443</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>158</v>
-      </c>
-      <c r="H77" s="13" t="n">
-        <v>69752277713.01001</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>139</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>65303843913</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="L77" s="13" t="n">
-        <v>4005987066</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="N77" s="13" t="n">
-        <v>36371935515</v>
+      <c r="N60" s="13" t="n">
+        <v>6660306992</v>
       </c>
     </row>
   </sheetData>
@@ -12078,7 +9494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14063,11 +11479,15 @@
           <t>Dinas Perhubungan - 2.15.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>3288788319</v>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
@@ -14109,11 +11529,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" s="11" t="n">
-        <v>3288788319</v>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -14335,11 +11759,15 @@
           <t>Dinas Pertanian - 3.27.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>2509875000</v>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
@@ -14381,11 +11809,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" s="11" t="n">
-        <v>2509875000</v>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -14884,7 +12316,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -14954,7 +12386,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -15024,7 +12456,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -15094,7 +12526,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -15164,7 +12596,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -15234,7 +12666,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -15304,7 +12736,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -15374,7 +12806,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -15444,48 +12876,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>83360000000</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>83360000000</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>8336802274</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>8336802274</v>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
@@ -15514,7 +12930,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -15584,7 +13000,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -15654,7 +13070,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -15724,7 +13140,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -15789,1221 +13205,51 @@
       </c>
     </row>
     <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>148497180038</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="F72" s="9" t="n">
-        <v>83360000000</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>8336802274</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>8336802274</v>
-      </c>
-      <c r="K72" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M72" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="N72" s="9" t="n">
-        <v>65137180038</v>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
-      <c r="A74" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N75" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C77" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="D77" s="13" t="n">
-        <v>268093404157</v>
-      </c>
-      <c r="E77" s="12" t="n">
+      <c r="C60" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>197157560800</v>
+      </c>
+      <c r="E60" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F60" s="13" t="n">
         <v>147115370800</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H77" s="13" t="n">
+      <c r="H60" s="13" t="n">
         <v>71235380008.97</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="I60" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J77" s="13" t="n">
+      <c r="J60" s="13" t="n">
         <v>71235380008.97</v>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="N77" s="13" t="n">
-        <v>120978033357</v>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>50042190000</v>
       </c>
     </row>
   </sheetData>
